--- a/artfynd/A 58701-2023 artfynd.xlsx
+++ b/artfynd/A 58701-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128547110</v>
       </c>
       <c r="B2" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>128547127</v>
       </c>
       <c r="B3" t="n">
-        <v>92252</v>
+        <v>92258</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 58701-2023 artfynd.xlsx
+++ b/artfynd/A 58701-2023 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>128547127</v>
       </c>
       <c r="B3" t="n">
-        <v>92258</v>
+        <v>92264</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 58701-2023 artfynd.xlsx
+++ b/artfynd/A 58701-2023 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>128547127</v>
       </c>
       <c r="B3" t="n">
-        <v>92264</v>
+        <v>92266</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 58701-2023 artfynd.xlsx
+++ b/artfynd/A 58701-2023 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>128547127</v>
       </c>
       <c r="B3" t="n">
-        <v>92266</v>
+        <v>92267</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 58701-2023 artfynd.xlsx
+++ b/artfynd/A 58701-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128547110</v>
       </c>
       <c r="B2" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>128547127</v>
       </c>
       <c r="B3" t="n">
-        <v>92267</v>
+        <v>92294</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 58701-2023 artfynd.xlsx
+++ b/artfynd/A 58701-2023 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>128547127</v>
       </c>
       <c r="B3" t="n">
-        <v>92294</v>
+        <v>92299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 58701-2023 artfynd.xlsx
+++ b/artfynd/A 58701-2023 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>128547127</v>
       </c>
       <c r="B3" t="n">
-        <v>92299</v>
+        <v>92304</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 58701-2023 artfynd.xlsx
+++ b/artfynd/A 58701-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128547110</v>
       </c>
       <c r="B2" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>128547127</v>
       </c>
       <c r="B3" t="n">
-        <v>92304</v>
+        <v>92308</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 58701-2023 artfynd.xlsx
+++ b/artfynd/A 58701-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128547110</v>
       </c>
       <c r="B2" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>128547127</v>
       </c>
       <c r="B3" t="n">
-        <v>92308</v>
+        <v>92313</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 58701-2023 artfynd.xlsx
+++ b/artfynd/A 58701-2023 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>128547127</v>
       </c>
       <c r="B3" t="n">
-        <v>92316</v>
+        <v>92321</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 58701-2023 artfynd.xlsx
+++ b/artfynd/A 58701-2023 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>128547127</v>
       </c>
       <c r="B3" t="n">
-        <v>92321</v>
+        <v>92329</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 58701-2023 artfynd.xlsx
+++ b/artfynd/A 58701-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128547110</v>
+        <v>128547127</v>
       </c>
       <c r="B2" t="n">
-        <v>57883</v>
+        <v>92732</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,31 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>2014</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) Pers.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,13 +713,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>767939</v>
+        <v>767985</v>
       </c>
       <c r="R2" t="n">
-        <v>7165206</v>
+        <v>7165194</v>
       </c>
       <c r="S2" t="n">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,7 +748,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +758,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128547127</v>
+        <v>128547110</v>
       </c>
       <c r="B3" t="n">
-        <v>92329</v>
+        <v>58114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,26 +796,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2014</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -828,13 +828,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>767985</v>
+        <v>767939</v>
       </c>
       <c r="R3" t="n">
-        <v>7165194</v>
+        <v>7165206</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 58701-2023 artfynd.xlsx
+++ b/artfynd/A 58701-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128547127</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -897,8 +907,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128547110</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>